--- a/output/2026_mladsi.xlsx
+++ b/output/2026_mladsi.xlsx
@@ -556,31 +556,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>3</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.7143</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4">
@@ -630,31 +630,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -667,31 +667,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J6" t="n">
         <v>2</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
@@ -707,26 +707,26 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -739,31 +739,31 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F8" t="n">
         <v>5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.7143</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3333</v>
       </c>
       <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" t="n">
         <v>6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -776,31 +776,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4286</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -828,10 +828,10 @@
         <v>5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.5714</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.7143</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
@@ -937,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1085,19 +1085,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Olšák Samuel</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>Procházková Emma</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Procházková Emma</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Procházková Emma</t>
+          <t>Brabec Marek</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1132,19 +1132,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Brabec Marek</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Procházková Emma</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Olšák Samuel</t>
-        </is>
-      </c>
       <c r="G4" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7143</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1152,15 +1152,15 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Procházková Emma</t>
+          <t>Brabec Marek</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1179,19 +1179,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brabec Marek</t>
+          <t>Procházková Emma</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Brabec Marek</t>
+          <t>Tříšková Adéla</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.7143</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1203,19 +1203,19 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Olšák Samuel</t>
+          <t>Tříšková Adéla</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Brabec Marek</t>
+          <t>Tříšková Adéla</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1238,11 +1238,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tříšková Adéla</t>
+          <t>Skopcová Laura</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Antošová Anna</t>
+          <t>Knapp Arnošt</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -1262,11 +1262,11 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Tříšková Adéla</t>
+          <t>Procházková Emma</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1293,27 +1293,27 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Procházková Emma</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Antošová Anna</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tříšková Adéla</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="n">
-        <v>0.4</v>
+        <v>0.4286</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tříšková Adéla</t>
+          <t>Olšák Samuel</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1348,23 +1348,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Skopcová Laura</t>
+          <t>Antošová Anna</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bohdanová Julie</t>
+          <t>Sršeň  Lukáš</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.4</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1380,15 +1380,15 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Hartman Zdeněk</t>
+          <t>Sršeň  Lukáš</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1399,23 +1399,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bohdanová Julie</t>
+          <t>Skopcová Laura</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bohdanová Julie</t>
+          <t>Hartman Zdeněk</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skopcová Laura</t>
+          <t>Tříšková Adéla</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -1427,23 +1427,23 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Bohdanová Julie</t>
+          <t>Skopcová Laura</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Bohdanová Julie</t>
+          <t>Knapp Arnošt</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1454,23 +1454,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Skopcová Laura</t>
+          <t>Sršeň  Lukáš</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hartman Zdeněk</t>
+          <t>Sršeň  Lukáš</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.25</v>
+        <v>0.3333</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seifrt Theodor</t>
+          <t>Bohdanová Julie</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -1478,15 +1478,15 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bohdanová Julie</t>
+          <t>Sršeň  Lukáš</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Skopcová Laura</t>
+          <t>Sršeň  Lukáš</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Skopcová Laura</t>
+          <t>Hartman Zdeněk</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1509,23 +1509,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Knapp Arnošt</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bohdanová Julie</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Seifrt Theodor</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Seifrt Theodor</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Sršeň  Lukáš</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
@@ -1533,23 +1533,23 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Seifrt Theodor</t>
+          <t>Skopcová Laura</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Seifrt Theodor</t>
+          <t>Knapp Arnošt</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Seifrt Theodor</t>
+          <t>Skopcová Laura</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -1564,31 +1564,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sršeň  Lukáš</t>
+          <t>Bohdanová Julie</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sršeň  Lukáš</t>
+          <t>Knapp Arnošt</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knapp Arnošt</t>
+          <t>Skopcová Laura</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.25</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Klusáková Barbora</t>
+          <t>Bohdanová Julie</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1596,15 +1596,15 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Sršeň  Lukáš</t>
+          <t>Bohdanová Julie</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sršeň  Lukáš</t>
+          <t>Bohdanová Julie</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Klusáková Barbora</t>
+          <t>Seifrt Theodor</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1627,15 +1627,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Seifrt Theodor</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Klusáková Barbora</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Hartman Zdeněk</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
@@ -1643,15 +1643,15 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Skopcová Laura</t>
+          <t>Seifrt Theodor</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Klusáková Barbora</t>
+          <t>Seifrt Theodor</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Klusáková Barbora</t>
+          <t>Seifrt Theodor</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Knapp Arnošt</t>
+          <t>Klusáková Barbora</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Knapp Arnošt</t>
+          <t>Klusáková Barbora</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -1690,23 +1690,23 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>Hartman Zdeněk</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>Klusáková Barbora</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sršeň  Lukáš</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Knapp Arnošt</t>
+          <t>Klusáková Barbora</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Knapp Arnošt</t>
+          <t>Klusáková Barbora</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1828,6 +1828,61 @@
         </is>
       </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1840,7 +1895,7 @@
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="F1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3:C16">
+  <conditionalFormatting sqref="C3:C17">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -1849,7 +1904,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E16">
+  <conditionalFormatting sqref="E3:E17">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1861,7 +1916,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G16">
+  <conditionalFormatting sqref="G3:G17">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1873,7 +1928,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K16">
+  <conditionalFormatting sqref="K3:K17">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -1882,7 +1937,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:M16">
+  <conditionalFormatting sqref="M3:M17">
     <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
@@ -2115,6 +2170,9 @@
       <c r="M4" t="n">
         <v>1</v>
       </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2162,6 +2220,12 @@
       <c r="M6" t="n">
         <v>0</v>
       </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2175,6 +2239,12 @@
       <c r="M7" t="n">
         <v>0</v>
       </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2185,6 +2255,9 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2225,6 +2298,12 @@
       <c r="M9" t="n">
         <v>1</v>
       </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2268,6 +2347,12 @@
       <c r="M10" t="n">
         <v>1</v>
       </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2310,6 +2395,12 @@
       </c>
       <c r="M11" t="n">
         <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2342,7 +2433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5274,6 +5365,486 @@
       <c r="H73" t="inlineStr">
         <is>
           <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>TSM Sokol Vysočany z.s.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>singl</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Brabec Marek</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>TSM Sokol Vysočany z.s.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>singl</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Hartman Zdeněk</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>TSM Sokol Vysočany z.s.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>singl</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knapp Arnošt</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>TSM Sokol Vysočany z.s.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>singl</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tříšková Adéla</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>TSM Sokol Vysočany z.s.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>singl</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Antošová Anna</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>TSM Sokol Vysočany z.s.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>singl</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Procházková Emma</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>TSM Sokol Vysočany z.s.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>debl</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knapp Arnošt</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Sršeň  Lukáš</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>TSM Sokol Vysočany z.s.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>debl</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Sršeň  Lukáš</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Knapp Arnošt</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>TSM Sokol Vysočany z.s.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>debl</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tříšková Adéla</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Procházková Emma</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>TSM Sokol Vysočany z.s.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>debl</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Procházková Emma</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tříšková Adéla</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>TSM Sokol Vysočany z.s.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>debl</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Antošová Anna</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hartman Zdeněk</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>TSM Sokol Vysočany z.s.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>debl</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Hartman Zdeněk</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Antošová Anna</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -5436,11 +6007,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Procházková Emma</t>
+          <t>Olšák Samuel</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -5448,7 +6019,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5475,7 +6046,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Procházková Emma</t>
+          <t>Brabec Marek</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5487,15 +6058,15 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.7143</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olšák Samuel</t>
+          <t>Procházková Emma</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7143</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -5503,7 +6074,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5511,7 +6082,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -5530,11 +6101,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brabec Marek</t>
+          <t>Procházková Emma</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5542,7 +6113,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.7143</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -5554,11 +6125,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Olšák Samuel</t>
+          <t>Tříšková Adéla</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5566,7 +6137,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -5589,19 +6160,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Procházková Emma</t>
+          <t>Antošová Anna</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.5714</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Antošová Anna</t>
+          <t>Knapp Arnošt</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -5613,11 +6184,11 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Procházková Emma</t>
+          <t>Antošová Anna</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -5644,27 +6215,27 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Antošová Anna</t>
+          <t>Procházková Emma</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sršeň  Lukáš</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tříšková Adéla</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0.4</v>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tříšková Adéla</t>
+          <t>Olšák Samuel</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -5672,11 +6243,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Antošová Anna</t>
+          <t>Procházková Emma</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -5695,43 +6266,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Seifrt Theodor</t>
+          <t>Knapp Arnošt</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Knapp Arnošt</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Seifrt Theodor</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Seifrt Theodor</t>
+          <t>Antošová Anna</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.4286</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Seifrt Theodor</t>
+          <t>Hartman Zdeněk</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Seifrt Theodor</t>
+          <t>Hartman Zdeněk</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -5754,7 +6325,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5762,39 +6333,39 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hartman Zdeněk</t>
+          <t>Seifrt Theodor</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hartman Zdeněk</t>
+          <t>Seifrt Theodor</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Hartman Zdeněk</t>
+          <t>Knapp Arnošt</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Hartman Zdeněk</t>
+          <t>Knapp Arnošt</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -5805,39 +6376,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Seifrt Theodor</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Seifrt Theodor</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tříšková Adéla</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>Knapp Arnošt</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Knapp Arnošt</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knapp Arnošt</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Knapp Arnošt</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Knapp Arnošt</t>
+          <t>Seifrt Theodor</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -5845,11 +6416,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Knapp Arnošt</t>
+          <t>Sršeň  Lukáš</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -5864,7 +6435,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5876,31 +6447,31 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>Hartman Zdeněk</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>Sršeň  Lukáš</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Sršeň  Lukáš</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Sršeň  Lukáš</t>
-        </is>
-      </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sršeň  Lukáš</t>
+          <t>Hartman Zdeněk</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -6032,7 +6603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6189,31 +6760,31 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
       <c r="K4" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -6226,31 +6797,31 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
       <c r="K5" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -6300,13 +6871,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -6401,8 +6972,45 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F10">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -6411,7 +7019,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G10">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -6420,7 +7028,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H10">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6432,7 +7040,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I10">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6444,7 +7052,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K9">
+  <conditionalFormatting sqref="K2:K10">
     <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
@@ -6463,7 +7071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6654,6 +7262,12 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6676,6 +7290,12 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6714,6 +7334,12 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6747,6 +7373,19 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6770,7 +7409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8105,6 +8744,326 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tenisová škola Lucie Hradecké z.s. B</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>singl</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sršeň  Lukáš</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tenisová škola Lucie Hradecké z.s. B</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>singl</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skopcová Laura</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Tenisová škola Lucie Hradecké z.s. B</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>singl</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Hobzová Magdalena</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tenisová škola Lucie Hradecké z.s. B</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>singl</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tenisová škola Lucie Hradecké z.s. B</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>debl</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sršeň  Lukáš</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Tenisová škola Lucie Hradecké z.s. B</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>debl</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sršeň  Lukáš</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tenisová škola Lucie Hradecké z.s. B</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>debl</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Skopcová Laura</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hobzová Magdalena</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tenisová škola Lucie Hradecké z.s. B</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>debl</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Hobzová Magdalena</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Skopcová Laura</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8116,7 +9075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8248,43 +9207,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Skopcová Laura</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Skopcová Laura</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Hartman Zdeněk</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Hartman Zdeněk</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Hartman Zdeněk</t>
-        </is>
-      </c>
       <c r="G3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bohdanová Julie</t>
+          <t>Skopcová Laura</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Hartman Zdeněk</t>
+          <t>Skopcová Laura</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -8303,7 +9262,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Skopcová Laura</t>
+          <t>Hartman Zdeněk</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -8311,7 +9270,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Skopcová Laura</t>
+          <t>Hartman Zdeněk</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -8327,15 +9286,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Knapp Arnošt</t>
+          <t>Sršeň  Lukáš</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Skopcová Laura</t>
+          <t>Hartman Zdeněk</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -8358,7 +9317,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bohdanová Julie</t>
+          <t>Sršeň  Lukáš</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -8366,7 +9325,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bohdanová Julie</t>
+          <t>Sršeň  Lukáš</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -8378,19 +9337,19 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Skopcová Laura</t>
+          <t>Bohdanová Julie</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Bohdanová Julie</t>
+          <t>Sršeň  Lukáš</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -8413,23 +9372,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Knapp Arnošt</t>
+          <t>Bohdanová Julie</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Knapp Arnošt</t>
+          <t>Bohdanová Julie</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skopcová Laura</t>
+          <t>Bohdanová Julie</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -8437,7 +9396,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Klusáková Barbora</t>
+          <t>Knapp Arnošt</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -8445,11 +9404,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Knapp Arnošt</t>
+          <t>Bohdanová Julie</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -8468,7 +9427,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sršeň  Lukáš</t>
+          <t>Knapp Arnošt</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -8476,7 +9435,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sršeň  Lukáš</t>
+          <t>Knapp Arnošt</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -8484,7 +9443,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bohdanová Julie</t>
+          <t>Klusáková Barbora</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
@@ -8492,15 +9451,15 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sršeň  Lukáš</t>
+          <t>Klusáková Barbora</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sršeň  Lukáš</t>
+          <t>Knapp Arnošt</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -8539,19 +9498,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klusáková Barbora</t>
+          <t>Skopcová Laura</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.25</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hartman Zdeněk</t>
+          <t>Hobzová Magdalena</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -8602,11 +9561,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hobzová Magdalena</t>
+          <t>Hartman Zdeněk</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -8677,6 +9636,61 @@
         </is>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>9.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8689,7 +9703,7 @@
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="F1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3:C10">
+  <conditionalFormatting sqref="C3:C11">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -8698,7 +9712,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E10">
+  <conditionalFormatting sqref="E3:E11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -8710,7 +9724,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G10">
+  <conditionalFormatting sqref="G3:G11">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -8722,7 +9736,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K10">
+  <conditionalFormatting sqref="K3:K11">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -8731,7 +9745,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:M10">
+  <conditionalFormatting sqref="M3:M11">
     <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
@@ -8750,7 +9764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8865,7 +9879,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Procházková Emma</t>
+          <t>Brabec Marek</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8874,28 +9888,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.7143</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.6</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
         <v>6.5</v>
@@ -8904,7 +9918,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brabec Marek</t>
+          <t>Procházková Emma</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8913,31 +9927,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.5714</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7143</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5">
@@ -8952,31 +9966,31 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
         <v>6</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" t="n">
         <v>5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.7143</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3333</v>
       </c>
       <c r="J5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" t="n">
         <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -8991,31 +10005,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4286</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
@@ -9030,37 +10044,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bohdanová Julie</t>
+          <t>Skopcová Laura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -9072,163 +10086,163 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
       <c r="K8" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Skopcová Laura</t>
+          <t>Sršeň  Lukáš</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A/B</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
         <v>2</v>
       </c>
-      <c r="D9" t="n">
+      <c r="H9" s="2" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Seifrt Theodor</t>
+          <t>Knapp Arnošt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A/B</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J10" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
       <c r="K10" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sršeň  Lukáš</t>
+          <t>Bohdanová Julie</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A/B</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>0.3333</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Klusáková Barbora</t>
+          <t>Seifrt Theodor</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A/B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>6</v>
@@ -9243,7 +10257,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.25</v>
+        <v>0.3333</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -9255,7 +10269,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Knapp Arnošt</t>
+          <t>Klusáková Barbora</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9264,13 +10278,13 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
         <v>4</v>
       </c>
-      <c r="D13" t="n">
-        <v>3</v>
-      </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -9282,7 +10296,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.25</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -9303,13 +10317,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -9369,8 +10383,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Janovský Pavel</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:F15">
+  <conditionalFormatting sqref="F2:F16">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -9379,7 +10432,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G15">
+  <conditionalFormatting sqref="G2:G16">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -9388,7 +10441,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H15">
+  <conditionalFormatting sqref="H2:H16">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -9400,7 +10453,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I15">
+  <conditionalFormatting sqref="I2:I16">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -9412,7 +10465,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K15">
+  <conditionalFormatting sqref="K2:K16">
     <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
